--- a/templates/ledger-akhir.xlsx
+++ b/templates/ledger-akhir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\school\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F0FC977A-8770-4EA6-9D25-980ACBDBD26F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EDAB41-6E97-4680-81FF-86E90C527995}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{6374E269-CC87-45C8-A59F-04766B4F347E}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>NO.</t>
   </si>
@@ -107,15 +106,6 @@
   </si>
   <si>
     <t>NH</t>
-  </si>
-  <si>
-    <t>UTS</t>
-  </si>
-  <si>
-    <t>UAS</t>
-  </si>
-  <si>
-    <t>Rpr</t>
   </si>
 </sst>
 </file>
@@ -261,7 +251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -312,35 +302,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" readingOrder="1"/>
@@ -438,12 +404,6 @@
     <xf numFmtId="1" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -453,6 +413,9 @@
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE38"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
@@ -788,14 +751,14 @@
     <col min="10" max="10" width="14.7109375" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" customWidth="1"/>
     <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="13" max="13" width="4.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="3.7109375" customWidth="1"/>
-    <col min="20" max="31" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" customWidth="1"/>
+    <col min="14" max="22" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.42578125" customWidth="1"/>
+    <col min="24" max="24" width="5" customWidth="1"/>
+    <col min="25" max="25" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -832,53 +795,45 @@
       <c r="L1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="9" t="s">
+      <c r="M1" s="30"/>
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="X1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="25"/>
       <c r="C2" s="26"/>
@@ -890,36 +845,26 @@
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-    </row>
-    <row r="3" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="31"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>1</v>
       </c>
@@ -933,28 +878,24 @@
       <c r="I3" s="17"/>
       <c r="J3" s="22"/>
       <c r="K3" s="23"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
       <c r="T3" s="18"/>
       <c r="U3" s="18"/>
       <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="18"/>
-      <c r="AB3" s="18"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-    </row>
-    <row r="4" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W3" s="19"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27">
         <v>2</v>
       </c>
@@ -968,28 +909,24 @@
       <c r="I4" s="17"/>
       <c r="J4" s="22"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
       <c r="T4" s="18"/>
       <c r="U4" s="18"/>
       <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="20"/>
-      <c r="AE4" s="20"/>
-    </row>
-    <row r="5" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W4" s="19"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27">
         <v>3</v>
       </c>
@@ -1003,28 +940,24 @@
       <c r="I5" s="17"/>
       <c r="J5" s="22"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
       <c r="T5" s="18"/>
       <c r="U5" s="18"/>
       <c r="V5" s="18"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="20"/>
-      <c r="AE5" s="20"/>
-    </row>
-    <row r="6" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W5" s="19"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <v>4</v>
       </c>
@@ -1038,28 +971,24 @@
       <c r="I6" s="17"/>
       <c r="J6" s="22"/>
       <c r="K6" s="23"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="U6" s="18"/>
       <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="18"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="20"/>
-      <c r="AE6" s="20"/>
-    </row>
-    <row r="7" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W6" s="19"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27">
         <v>5</v>
       </c>
@@ -1073,28 +1002,24 @@
       <c r="I7" s="17"/>
       <c r="J7" s="22"/>
       <c r="K7" s="23"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
       <c r="T7" s="18"/>
       <c r="U7" s="18"/>
       <c r="V7" s="18"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="18"/>
-      <c r="AB7" s="18"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="20"/>
-      <c r="AE7" s="20"/>
-    </row>
-    <row r="8" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W7" s="19"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27">
         <v>6</v>
       </c>
@@ -1108,28 +1033,24 @@
       <c r="I8" s="17"/>
       <c r="J8" s="22"/>
       <c r="K8" s="23"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
       <c r="T8" s="18"/>
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="18"/>
-      <c r="AB8" s="18"/>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="20"/>
-      <c r="AE8" s="20"/>
-    </row>
-    <row r="9" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W8" s="19"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27">
         <v>7</v>
       </c>
@@ -1143,28 +1064,24 @@
       <c r="I9" s="17"/>
       <c r="J9" s="22"/>
       <c r="K9" s="23"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
-    </row>
-    <row r="10" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W9" s="19"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
         <v>8</v>
       </c>
@@ -1178,28 +1095,24 @@
       <c r="I10" s="17"/>
       <c r="J10" s="22"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="18"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="20"/>
-    </row>
-    <row r="11" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W10" s="19"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27">
         <v>9</v>
       </c>
@@ -1213,28 +1126,24 @@
       <c r="I11" s="17"/>
       <c r="J11" s="22"/>
       <c r="K11" s="23"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="18"/>
-      <c r="Y11" s="18"/>
-      <c r="Z11" s="18"/>
-      <c r="AA11" s="18"/>
-      <c r="AB11" s="18"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="20"/>
-      <c r="AE11" s="20"/>
-    </row>
-    <row r="12" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W11" s="19"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27">
         <v>10</v>
       </c>
@@ -1248,28 +1157,24 @@
       <c r="I12" s="17"/>
       <c r="J12" s="22"/>
       <c r="K12" s="23"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
-      <c r="W12" s="18"/>
-      <c r="X12" s="18"/>
-      <c r="Y12" s="18"/>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="20"/>
-      <c r="AE12" s="20"/>
-    </row>
-    <row r="13" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W12" s="19"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27">
         <v>11</v>
       </c>
@@ -1283,28 +1188,24 @@
       <c r="I13" s="17"/>
       <c r="J13" s="22"/>
       <c r="K13" s="23"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="18"/>
-      <c r="Y13" s="18"/>
-      <c r="Z13" s="18"/>
-      <c r="AA13" s="18"/>
-      <c r="AB13" s="18"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="20"/>
-      <c r="AE13" s="20"/>
-    </row>
-    <row r="14" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W13" s="19"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27">
         <v>12</v>
       </c>
@@ -1318,28 +1219,24 @@
       <c r="I14" s="17"/>
       <c r="J14" s="22"/>
       <c r="K14" s="23"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="18"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="20"/>
-    </row>
-    <row r="15" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W14" s="19"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27">
         <v>13</v>
       </c>
@@ -1353,28 +1250,24 @@
       <c r="I15" s="17"/>
       <c r="J15" s="22"/>
       <c r="K15" s="23"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
-      <c r="W15" s="18"/>
-      <c r="X15" s="18"/>
-      <c r="Y15" s="18"/>
-      <c r="Z15" s="18"/>
-      <c r="AA15" s="18"/>
-      <c r="AB15" s="18"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
-    </row>
-    <row r="16" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W15" s="19"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27">
         <v>14</v>
       </c>
@@ -1388,28 +1281,24 @@
       <c r="I16" s="17"/>
       <c r="J16" s="22"/>
       <c r="K16" s="23"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="18"/>
-      <c r="Y16" s="18"/>
-      <c r="Z16" s="18"/>
-      <c r="AA16" s="18"/>
-      <c r="AB16" s="18"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="20"/>
-    </row>
-    <row r="17" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W16" s="19"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27">
         <v>15</v>
       </c>
@@ -1423,28 +1312,24 @@
       <c r="I17" s="17"/>
       <c r="J17" s="22"/>
       <c r="K17" s="23"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="18"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="20"/>
-      <c r="AE17" s="20"/>
-    </row>
-    <row r="18" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W17" s="19"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>16</v>
       </c>
@@ -1458,28 +1343,24 @@
       <c r="I18" s="17"/>
       <c r="J18" s="22"/>
       <c r="K18" s="23"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18"/>
       <c r="T18" s="18"/>
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="18"/>
-      <c r="Z18" s="18"/>
-      <c r="AA18" s="18"/>
-      <c r="AB18" s="18"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="20"/>
-      <c r="AE18" s="20"/>
-    </row>
-    <row r="19" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W18" s="19"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27">
         <v>17</v>
       </c>
@@ -1493,28 +1374,24 @@
       <c r="I19" s="17"/>
       <c r="J19" s="22"/>
       <c r="K19" s="23"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
       <c r="T19" s="18"/>
       <c r="U19" s="18"/>
       <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="18"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="20"/>
-      <c r="AE19" s="20"/>
-    </row>
-    <row r="20" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W19" s="19"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27">
         <v>18</v>
       </c>
@@ -1528,28 +1405,24 @@
       <c r="I20" s="17"/>
       <c r="J20" s="22"/>
       <c r="K20" s="23"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
       <c r="T20" s="18"/>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="18"/>
-      <c r="AC20" s="19"/>
-      <c r="AD20" s="20"/>
-      <c r="AE20" s="20"/>
-    </row>
-    <row r="21" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W20" s="19"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27">
         <v>19</v>
       </c>
@@ -1563,28 +1436,24 @@
       <c r="I21" s="17"/>
       <c r="J21" s="22"/>
       <c r="K21" s="23"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
       <c r="T21" s="18"/>
       <c r="U21" s="18"/>
       <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="20"/>
-    </row>
-    <row r="22" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W21" s="19"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="27">
         <v>20</v>
       </c>
@@ -1598,28 +1467,24 @@
       <c r="I22" s="17"/>
       <c r="J22" s="22"/>
       <c r="K22" s="23"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
       <c r="T22" s="18"/>
       <c r="U22" s="18"/>
       <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="18"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="20"/>
-      <c r="AE22" s="20"/>
-    </row>
-    <row r="23" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W22" s="19"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27">
         <v>21</v>
       </c>
@@ -1633,28 +1498,24 @@
       <c r="I23" s="17"/>
       <c r="J23" s="22"/>
       <c r="K23" s="23"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
       <c r="T23" s="18"/>
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="20"/>
-      <c r="AE23" s="20"/>
-    </row>
-    <row r="24" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W23" s="19"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27">
         <v>22</v>
       </c>
@@ -1668,28 +1529,24 @@
       <c r="I24" s="17"/>
       <c r="J24" s="22"/>
       <c r="K24" s="23"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
       <c r="T24" s="18"/>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="20"/>
-      <c r="AE24" s="20"/>
-    </row>
-    <row r="25" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W24" s="19"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="27">
         <v>23</v>
       </c>
@@ -1703,28 +1560,24 @@
       <c r="I25" s="17"/>
       <c r="J25" s="22"/>
       <c r="K25" s="23"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
       <c r="T25" s="18"/>
       <c r="U25" s="18"/>
       <c r="V25" s="18"/>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="20"/>
-      <c r="AE25" s="20"/>
-    </row>
-    <row r="26" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W25" s="19"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27">
         <v>24</v>
       </c>
@@ -1738,28 +1591,24 @@
       <c r="I26" s="17"/>
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
       <c r="T26" s="18"/>
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="19"/>
-      <c r="AD26" s="20"/>
-      <c r="AE26" s="20"/>
-    </row>
-    <row r="27" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W26" s="19"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27">
         <v>25</v>
       </c>
@@ -1773,28 +1622,24 @@
       <c r="I27" s="17"/>
       <c r="J27" s="22"/>
       <c r="K27" s="23"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
       <c r="T27" s="18"/>
       <c r="U27" s="18"/>
       <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="19"/>
-      <c r="AD27" s="20"/>
-      <c r="AE27" s="20"/>
-    </row>
-    <row r="28" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W27" s="19"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27">
         <v>26</v>
       </c>
@@ -1808,28 +1653,24 @@
       <c r="I28" s="17"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
       <c r="T28" s="18"/>
       <c r="U28" s="18"/>
       <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="19"/>
-      <c r="AD28" s="20"/>
-      <c r="AE28" s="20"/>
-    </row>
-    <row r="29" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W28" s="19"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27">
         <v>27</v>
       </c>
@@ -1843,28 +1684,24 @@
       <c r="I29" s="17"/>
       <c r="J29" s="22"/>
       <c r="K29" s="23"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
       <c r="T29" s="18"/>
       <c r="U29" s="18"/>
       <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="20"/>
-      <c r="AE29" s="20"/>
-    </row>
-    <row r="30" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W29" s="19"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27">
         <v>28</v>
       </c>
@@ -1878,28 +1715,24 @@
       <c r="I30" s="17"/>
       <c r="J30" s="22"/>
       <c r="K30" s="23"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
       <c r="T30" s="18"/>
       <c r="U30" s="18"/>
       <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="19"/>
-      <c r="AD30" s="20"/>
-      <c r="AE30" s="20"/>
-    </row>
-    <row r="31" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W30" s="19"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="27">
         <v>29</v>
       </c>
@@ -1913,28 +1746,24 @@
       <c r="I31" s="17"/>
       <c r="J31" s="22"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
       <c r="T31" s="18"/>
       <c r="U31" s="18"/>
       <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
-      <c r="AA31" s="18"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="20"/>
-      <c r="AE31" s="20"/>
-    </row>
-    <row r="32" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W31" s="19"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27">
         <v>30</v>
       </c>
@@ -1948,28 +1777,24 @@
       <c r="I32" s="17"/>
       <c r="J32" s="22"/>
       <c r="K32" s="23"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
       <c r="T32" s="18"/>
       <c r="U32" s="18"/>
       <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
-      <c r="AA32" s="18"/>
-      <c r="AB32" s="18"/>
-      <c r="AC32" s="19"/>
-      <c r="AD32" s="20"/>
-      <c r="AE32" s="20"/>
-    </row>
-    <row r="33" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W32" s="19"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="27">
         <v>31</v>
       </c>
@@ -1983,28 +1808,24 @@
       <c r="I33" s="17"/>
       <c r="J33" s="22"/>
       <c r="K33" s="23"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="18"/>
       <c r="T33" s="18"/>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="19"/>
-      <c r="AD33" s="20"/>
-      <c r="AE33" s="20"/>
-    </row>
-    <row r="34" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W33" s="19"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="27">
         <v>32</v>
       </c>
@@ -2018,28 +1839,24 @@
       <c r="I34" s="17"/>
       <c r="J34" s="22"/>
       <c r="K34" s="23"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
       <c r="T34" s="18"/>
       <c r="U34" s="18"/>
       <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="19"/>
-      <c r="AD34" s="20"/>
-      <c r="AE34" s="20"/>
-    </row>
-    <row r="35" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W34" s="19"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27">
         <v>33</v>
       </c>
@@ -2053,28 +1870,24 @@
       <c r="I35" s="17"/>
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35"/>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
       <c r="T35" s="18"/>
       <c r="U35" s="18"/>
       <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="19"/>
-      <c r="AD35" s="20"/>
-      <c r="AE35" s="20"/>
-    </row>
-    <row r="36" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W35" s="19"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="27">
         <v>34</v>
       </c>
@@ -2088,28 +1901,24 @@
       <c r="I36" s="17"/>
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
       <c r="T36" s="18"/>
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18"/>
-      <c r="AB36" s="18"/>
-      <c r="AC36" s="19"/>
-      <c r="AD36" s="20"/>
-      <c r="AE36" s="20"/>
-    </row>
-    <row r="37" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W36" s="19"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="27">
         <v>35</v>
       </c>
@@ -2123,28 +1932,24 @@
       <c r="I37" s="17"/>
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
       <c r="T37" s="18"/>
       <c r="U37" s="18"/>
       <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18"/>
-      <c r="AB37" s="18"/>
-      <c r="AC37" s="19"/>
-      <c r="AD37" s="20"/>
-      <c r="AE37" s="20"/>
-    </row>
-    <row r="38" spans="1:31" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" s="21" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
